--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104624_W19.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104624_W19.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0941</v>
+        <v>3.5598</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9271</v>
+        <v>7.0407</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.833</v>
+        <v>-3.4809</v>
       </c>
       <c r="G2" t="n">
-        <v>3.5942</v>
+        <v>3.6119</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4201</v>
+        <v>-0.4058</v>
       </c>
       <c r="I2" t="n">
-        <v>4.0143</v>
+        <v>4.0176</v>
       </c>
       <c r="J2" t="n">
-        <v>6.5402</v>
+        <v>6.5217</v>
       </c>
       <c r="K2" t="n">
-        <v>1.8009</v>
+        <v>1.7926</v>
       </c>
       <c r="L2" t="n">
-        <v>4.7392</v>
+        <v>4.7291</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.946</v>
+        <v>-2.9098</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.2211</v>
+        <v>-2.1984</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7249</v>
+        <v>-0.7114</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5928</v>
+        <v>-0.1416</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1179</v>
+        <v>0.0229</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4748</v>
+        <v>-0.1645</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W2" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3925</v>
+        <v>0.9628</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6196</v>
+        <v>1.9295</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2271</v>
+        <v>-0.9668</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.4075</v>
+        <v>-0.4085</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1141</v>
+        <v>2.1057</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.5215</v>
+        <v>-2.5141</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1713</v>
+        <v>2.1409</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5948</v>
+        <v>3.5713</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.4234</v>
+        <v>-1.4303</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.5788</v>
+        <v>-2.5494</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4807</v>
+        <v>-1.4656</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0981</v>
+        <v>-1.0838</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1629</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4688</v>
+        <v>-0.1141</v>
       </c>
       <c r="U3" t="n">
-        <v>1.6317</v>
+        <v>0.8495</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3176</v>
+        <v>1.3187</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. KURUCS</t>
+          <t>D. MAVRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4968</v>
+        <v>0.7635</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1152</v>
+        <v>2.3677</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3816</v>
+        <v>-1.6042</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1054</v>
+        <v>3.6587</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.1285</v>
+        <v>2.7407</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0231</v>
+        <v>0.918</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8443000000000001</v>
+        <v>6.1515</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.5683</v>
+        <v>4.3642</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4126</v>
+        <v>1.7874</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9497</v>
+        <v>-2.4929</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.5602</v>
+        <v>-1.6235</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6105</v>
+        <v>-0.8694</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.0415</v>
+        <v>-3.8697</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.4025</v>
+        <v>-4.5526</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0047</v>
+        <v>-0.1149</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0344</v>
+        <v>-0.3207</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0297</v>
+        <v>0.2058</v>
       </c>
       <c r="V4" t="n">
-        <v>1.639</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>1.639</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1837</v>
+        <v>0.3183</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3628</v>
+        <v>0.4294</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1791</v>
+        <v>-0.1111</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3506</v>
+        <v>0.3531</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1933</v>
+        <v>0.1952</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5715</v>
+        <v>0.5688</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5715</v>
+        <v>0.5688</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2209</v>
+        <v>-0.2157</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3781</v>
+        <v>-0.3736</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1669</v>
+        <v>-0.0349</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2087</v>
+        <v>-0.1394</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0417</v>
+        <v>0.1046</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,22 +877,22 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -904,13 +904,13 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. MAVRA</t>
+          <t>A. KURUCS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0723</v>
+        <v>-0.0892</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1125</v>
+        <v>-0.4425</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.0402</v>
+        <v>0.3533</v>
       </c>
       <c r="G7" t="n">
-        <v>3.6624</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7534</v>
+        <v>-2.1173</v>
       </c>
       <c r="I7" t="n">
-        <v>0.909</v>
+        <v>2.0198</v>
       </c>
       <c r="J7" t="n">
-        <v>6.1825</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>4.3913</v>
+        <v>-0.5795</v>
       </c>
       <c r="L7" t="n">
-        <v>1.7912</v>
+        <v>1.3997</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.5202</v>
+        <v>-0.9177</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.638</v>
+        <v>-1.5378</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8822</v>
+        <v>0.6201</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.8562</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.5367</v>
+        <v>-3.4145</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8266</v>
+        <v>0.4228</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6261</v>
+        <v>0.5177</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2005</v>
+        <v>-0.0948</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0927</v>
+        <v>1.6342</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0927</v>
+        <v>1.6342</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ARANITOVIC</t>
+          <t>J. SAKHO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1322</v>
+        <v>-1.4586</v>
       </c>
       <c r="E8" t="n">
-        <v>2.9286</v>
+        <v>-0.2335</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.0609</v>
+        <v>-1.2251</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8699</v>
+        <v>-0.8084</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.547</v>
+        <v>-0.983</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6771</v>
+        <v>0.1746</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1775</v>
+        <v>0.3241</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4991</v>
+        <v>0.1379</v>
       </c>
       <c r="L8" t="n">
-        <v>1.6765</v>
+        <v>0.1862</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.0473</v>
+        <v>-1.1325</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.0479</v>
+        <v>-1.1209</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9994</v>
+        <v>-0.0116</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.3352</v>
+        <v>0.4879</v>
       </c>
       <c r="T8" t="n">
-        <v>1.7512</v>
+        <v>0.5805</v>
       </c>
       <c r="U8" t="n">
-        <v>0.584</v>
+        <v>-0.0926</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.7317</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.7317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. SAKHO</t>
+          <t>A. ARANITOVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2942</v>
+        <v>-2.0509</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3009</v>
+        <v>1.9909</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9933</v>
+        <v>-4.0418</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8279</v>
+        <v>-1.851</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9958</v>
+        <v>-2.5366</v>
       </c>
       <c r="I9" t="n">
-        <v>0.168</v>
+        <v>0.6856</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3251</v>
+        <v>1.1574</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1385</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1866</v>
+        <v>1.668</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.153</v>
+        <v>-3.0084</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1344</v>
+        <v>-2.026</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0186</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6677999999999999</v>
+        <v>1.3857</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5081</v>
+        <v>0.8335</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1597</v>
+        <v>0.5521</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.7237</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. COOK</t>
+          <t>F. ALONSO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0172</v>
+        <v>-2.2632</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2582</v>
+        <v>-0.7040999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.759</v>
+        <v>-1.5591</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.5536</v>
+        <v>-6.0566</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.7216</v>
+        <v>-2.0479</v>
       </c>
       <c r="I10" t="n">
-        <v>0.168</v>
+        <v>-4.0087</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5162</v>
+        <v>-3.0479</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.0359</v>
+        <v>-0.5968</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5197000000000001</v>
+        <v>-2.4511</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.0374</v>
+        <v>-3.0087</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6857</v>
+        <v>-1.4511</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3517</v>
+        <v>-1.5576</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6805</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6705</v>
+        <v>0.525</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2994</v>
+        <v>0.2135</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3711</v>
+        <v>0.3115</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5463</v>
+        <v>3.2684</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>3.2684</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. ALONSO</t>
+          <t>K. COOK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1726</v>
+        <v>-2.3418</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2079</v>
+        <v>-0.3967</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9647</v>
+        <v>-1.9451</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.0568</v>
+        <v>-2.5372</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.0505</v>
+        <v>-2.7118</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.0063</v>
+        <v>0.1746</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.0221</v>
+        <v>-0.5313</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5857</v>
+        <v>-1.0449</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.4364</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.0347</v>
+        <v>-2.0059</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4648</v>
+        <v>-1.6668</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.5699</v>
+        <v>-0.3391</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3938</v>
+        <v>0.3335</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3297</v>
+        <v>0.1833</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0641</v>
+        <v>0.1503</v>
       </c>
       <c r="V11" t="n">
-        <v>3.278</v>
+        <v>0.5447</v>
       </c>
       <c r="W11" t="n">
-        <v>3.278</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3798</v>
+        <v>-3.4454</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3609</v>
+        <v>-1.6461</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0189</v>
+        <v>-1.7993</v>
       </c>
       <c r="G12" t="n">
-        <v>2.2071</v>
+        <v>2.1896</v>
       </c>
       <c r="H12" t="n">
-        <v>2.1805</v>
+        <v>2.169</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0266</v>
+        <v>0.0206</v>
       </c>
       <c r="J12" t="n">
-        <v>3.6396</v>
+        <v>3.5943</v>
       </c>
       <c r="K12" t="n">
-        <v>3.5357</v>
+        <v>3.5056</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1038</v>
+        <v>0.0887</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.4325</v>
+        <v>-1.4047</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3552</v>
+        <v>-1.3365</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.6708</v>
+        <v>-5.6908</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7307</v>
+        <v>0.2347</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3297</v>
+        <v>0.4504</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4011</v>
+        <v>-0.2157</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.599299999999999</v>
+        <v>-5.886799999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>9.937899999999999</v>
+        <v>10.3353</v>
       </c>
       <c r="F13" t="n">
-        <v>-16.5373</v>
+        <v>-16.2222</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.849499999999999</v>
+        <v>-1.788100000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.6222</v>
+        <v>-3.591800000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7729</v>
+        <v>1.8038</v>
       </c>
       <c r="J13" t="n">
-        <v>17.9137</v>
+        <v>17.6996</v>
       </c>
       <c r="K13" t="n">
-        <v>11.3437</v>
+        <v>11.2086</v>
       </c>
       <c r="L13" t="n">
-        <v>6.5698</v>
+        <v>6.4913</v>
       </c>
       <c r="M13" t="n">
-        <v>-19.7632</v>
+        <v>-19.4878</v>
       </c>
       <c r="N13" t="n">
-        <v>-14.9661</v>
+        <v>-14.8002</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.7969</v>
+        <v>-4.6875</v>
       </c>
       <c r="P13" t="n">
-        <v>-12.4759</v>
+        <v>-12.5198</v>
       </c>
       <c r="Q13" t="n">
-        <v>-20.4151</v>
+        <v>-20.487</v>
       </c>
       <c r="R13" t="n">
-        <v>7.9392</v>
+        <v>7.967200000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>3.130299999999999</v>
+        <v>3.8336</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5122</v>
+        <v>2.2276</v>
       </c>
       <c r="U13" t="n">
-        <v>1.618</v>
+        <v>1.6062</v>
       </c>
       <c r="V13" t="n">
-        <v>4.5955</v>
+        <v>4.587</v>
       </c>
       <c r="W13" t="n">
-        <v>10.9267</v>
+        <v>10.8947</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.3312</v>
+        <v>-6.3077</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.9135</v>
+        <v>5.6592</v>
       </c>
       <c r="E14" t="n">
-        <v>8.3599</v>
+        <v>7.0056</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4465</v>
+        <v>-1.3464</v>
       </c>
       <c r="G14" t="n">
-        <v>3.501</v>
+        <v>3.4725</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9225</v>
+        <v>2.8883</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5785</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>4.6917</v>
+        <v>4.6458</v>
       </c>
       <c r="K14" t="n">
-        <v>3.3483</v>
+        <v>3.3053</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3434</v>
+        <v>1.3405</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.1908</v>
+        <v>-1.1733</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5978</v>
+        <v>0.3657</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5243</v>
+        <v>0.2296</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0735</v>
+        <v>0.1361</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="15">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3719</v>
+        <v>2.9445</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2991</v>
+        <v>1.8662</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0728</v>
+        <v>1.0783</v>
       </c>
       <c r="G15" t="n">
-        <v>1.626</v>
+        <v>1.6345</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3115</v>
+        <v>1.3186</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6158</v>
+        <v>3.5971</v>
       </c>
       <c r="K15" t="n">
-        <v>1.638</v>
+        <v>1.6235</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9778</v>
+        <v>1.9736</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9897</v>
+        <v>-1.9626</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3234</v>
+        <v>-1.3077</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P15" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2957</v>
+        <v>-0.7387</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1825</v>
+        <v>-0.5927</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1131</v>
+        <v>-0.146</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1071</v>
+        <v>1.7851</v>
       </c>
       <c r="E16" t="n">
-        <v>1.353</v>
+        <v>1.9044</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2459</v>
+        <v>-0.1194</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4569</v>
+        <v>0.453</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3983</v>
+        <v>0.3964</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0586</v>
+        <v>0.0565</v>
       </c>
       <c r="J16" t="n">
-        <v>3.2757</v>
+        <v>3.2473</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8631</v>
+        <v>1.8476</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4126</v>
+        <v>1.3997</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.8188</v>
+        <v>-2.7943</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4648</v>
+        <v>-1.4511</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.354</v>
+        <v>-1.3432</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6693</v>
+        <v>0.015</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.747</v>
+        <v>-0.156</v>
       </c>
       <c r="U16" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.171</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0245</v>
+        <v>0.9579</v>
       </c>
       <c r="E17" t="n">
-        <v>2.7117</v>
+        <v>2.4335</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.6872</v>
+        <v>-1.4756</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1443</v>
+        <v>1.1257</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1977</v>
+        <v>1.1949</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0534</v>
+        <v>-0.0692</v>
       </c>
       <c r="J17" t="n">
-        <v>2.4386</v>
+        <v>2.4017</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0016</v>
+        <v>1.9855</v>
       </c>
       <c r="L17" t="n">
-        <v>0.437</v>
+        <v>0.4162</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2944</v>
+        <v>-1.2759</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P17" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7095</v>
+        <v>-0.7597</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0484</v>
+        <v>-0.2837</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6611</v>
+        <v>-0.476</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. CATE</t>
+          <t>J. RADEBAUGH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9052</v>
+        <v>0.8413</v>
       </c>
       <c r="E18" t="n">
-        <v>4.1293</v>
+        <v>1.8166</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.2241</v>
+        <v>-0.9752999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9116</v>
+        <v>1.2073</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2741</v>
+        <v>-0.4081</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3625</v>
+        <v>1.6154</v>
       </c>
       <c r="J18" t="n">
-        <v>3.3036</v>
+        <v>2.2977</v>
       </c>
       <c r="K18" t="n">
-        <v>3.117</v>
+        <v>0.7272</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1866</v>
+        <v>1.5705</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.392</v>
+        <v>-1.0904</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.8429</v>
+        <v>-1.1353</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.549</v>
+        <v>0.0449</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4984</v>
+        <v>-0.8699</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8257</v>
+        <v>-0.4811</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3273</v>
+        <v>-0.3888</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.639</v>
+        <v>-1.0895</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.639</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. RADEBAUGH</t>
+          <t>E. CATE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3065</v>
+        <v>0.2796</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4966</v>
+        <v>3.4092</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.19</v>
+        <v>-3.1296</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2211</v>
+        <v>0.9221</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4128</v>
+        <v>1.2779</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6338</v>
+        <v>-0.3557</v>
       </c>
       <c r="J19" t="n">
-        <v>2.3313</v>
+        <v>3.2888</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7375</v>
+        <v>3.1026</v>
       </c>
       <c r="L19" t="n">
-        <v>1.5938</v>
+        <v>0.1862</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1103</v>
+        <v>-2.3667</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1503</v>
+        <v>-1.8248</v>
       </c>
       <c r="O19" t="n">
-        <v>0.04</v>
+        <v>-0.5419</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4097</v>
+        <v>-0.1465</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8347</v>
+        <v>0.1204</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.575</v>
+        <v>-0.2669</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0927</v>
+        <v>-1.6342</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0927</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. RAIESTE</t>
+          <t>T. NAKIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1486</v>
+        <v>-0.3279</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3496</v>
+        <v>0.1944</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.201</v>
+        <v>-0.5223</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.1779</v>
+        <v>-1.4728</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5036</v>
+        <v>0.4044</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.6815</v>
+        <v>-1.8772</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9445</v>
+        <v>0.1739</v>
       </c>
       <c r="K20" t="n">
-        <v>2.3307</v>
+        <v>1.3962</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3861</v>
+        <v>-1.2223</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.1224</v>
+        <v>-1.6467</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.827</v>
+        <v>-0.9918</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2954</v>
+        <v>-0.6549</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2268</v>
+        <v>3.4145</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>3.4145</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4606</v>
+        <v>-0.0907</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0998</v>
+        <v>0.0205</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5604</v>
+        <v>-0.1111</v>
       </c>
       <c r="V20" t="n">
-        <v>1.639</v>
+        <v>-2.1789</v>
       </c>
       <c r="W20" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. NAKIC</t>
+          <t>S. RAIESTE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6263</v>
+        <v>-0.3792</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0979</v>
+        <v>1.1995</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7242</v>
+        <v>-1.5787</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4775</v>
+        <v>-2.1771</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3938</v>
+        <v>0.5027</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.8712</v>
+        <v>-2.6797</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1977</v>
+        <v>0.9199000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>1.4027</v>
+        <v>2.313</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.205</v>
+        <v>-1.3931</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6752</v>
+        <v>-3.097</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0089</v>
+        <v>-1.8103</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6663</v>
+        <v>-1.2866</v>
       </c>
       <c r="P21" t="n">
-        <v>3.4025</v>
+        <v>0.2276</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>3.4025</v>
+        <v>1.3658</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.366</v>
+        <v>-0.064</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0998</v>
+        <v>-0.2164</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2662</v>
+        <v>0.1524</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.1853</v>
+        <v>1.6342</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.6342</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.308</v>
+        <v>-2.1223</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9058</v>
+        <v>-0.7914</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4022</v>
+        <v>-1.3309</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7289</v>
+        <v>-0.7296</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0202</v>
+        <v>0.0228</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6971000000000001</v>
+        <v>-0.7007</v>
       </c>
       <c r="K22" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1669</v>
+        <v>0.0139</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2087</v>
+        <v>-0.0907</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0417</v>
+        <v>0.1046</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="23">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2435</v>
+        <v>-2.2646</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3541</v>
+        <v>-2.816</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1106</v>
+        <v>0.5514</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.6271</v>
+        <v>-2.6477</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.9896</v>
+        <v>-3.0034</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3625</v>
+        <v>0.3557</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.3387</v>
+        <v>-0.3837</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.5248</v>
+        <v>-1.5523</v>
       </c>
       <c r="L23" t="n">
-        <v>1.186</v>
+        <v>1.1686</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.2884</v>
+        <v>-2.264</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4648</v>
+        <v>-1.4511</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.07</v>
+        <v>-0.0721</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.747</v>
+        <v>-0.156</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.323</v>
+        <v>0.0838</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>6.599499999999998</v>
+        <v>7.373600000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>16.5372</v>
+        <v>16.222</v>
       </c>
       <c r="F24" t="n">
-        <v>-9.937700000000001</v>
+        <v>-8.8485</v>
       </c>
       <c r="G24" t="n">
-        <v>1.849499999999999</v>
+        <v>1.787900000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>3.622300000000001</v>
+        <v>3.5918</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.772699999999999</v>
+        <v>-1.803799999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>19.7631</v>
+        <v>19.4878</v>
       </c>
       <c r="K24" t="n">
-        <v>14.9661</v>
+        <v>14.8003</v>
       </c>
       <c r="L24" t="n">
-        <v>4.7971</v>
+        <v>4.6875</v>
       </c>
       <c r="M24" t="n">
-        <v>-17.9138</v>
+        <v>-17.6998</v>
       </c>
       <c r="N24" t="n">
-        <v>-11.3436</v>
+        <v>-11.2085</v>
       </c>
       <c r="O24" t="n">
-        <v>-6.5699</v>
+        <v>-6.4912</v>
       </c>
       <c r="P24" t="n">
-        <v>12.4758</v>
+        <v>12.5198</v>
       </c>
       <c r="Q24" t="n">
-        <v>-7.9392</v>
+        <v>-7.9672</v>
       </c>
       <c r="R24" t="n">
-        <v>20.415</v>
+        <v>20.4868</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.1303</v>
+        <v>-2.347</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.6179</v>
+        <v>-1.6061</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.5124</v>
+        <v>-0.7408999999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>-4.595499999999999</v>
+        <v>-4.587</v>
       </c>
       <c r="W24" t="n">
-        <v>6.3311</v>
+        <v>6.3076</v>
       </c>
       <c r="X24" t="n">
-        <v>-10.9267</v>
+        <v>-10.8947</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104624_W19.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104624_W19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104624_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104624_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104624_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104624_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104624_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104624_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104624_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104624_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104624_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104624_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104624_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-6.3077</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104624_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104624_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104624_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104624_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104624_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104624_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104624_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104624_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104624_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104624_W19.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-10.8947</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
